--- a/V5.0_双人执行工作区/00_共享/模型交接/FIELD_DICTIONARY_V50.xlsx
+++ b/V5.0_双人执行工作区/00_共享/模型交接/FIELD_DICTIONARY_V50.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R408a8d6a17c743d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="2" r:id="Rd925bc4c7b064146"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面字段测试" sheetId="3" r:id="R2f582b39061b474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rae7e8e5cf8b14f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段字典" sheetId="2" r:id="R304fb87d31744c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面字段测试" sheetId="3" r:id="R61bd24b1f53a4206"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,19 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF166534"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF166534"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -102,6 +113,11 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -109,7 +125,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -158,6 +174,18 @@
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -169,7 +197,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -180,7 +208,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -191,7 +219,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -202,7 +230,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -213,7 +241,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -224,7 +252,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -235,7 +263,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -246,7 +274,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -18159,7 +18187,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>页面3/5/6字段测试｜B账号必须只读查询</x:v>
+        <x:v>页面3/5/6字段树核对｜项目共用Smartbi账号</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -18170,20 +18198,20 @@
       <x:c r="H1" s="3"/>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>状态：BLOCKED｜仅完成离线预审与交付模板；Smartbi关系、指标、权限、截图、冻结和A/B签收必须人工完成。</x:v>
-      </x:c>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2" s="6"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2" s="6"/>
-      <x:c r="F2" s="6"/>
-      <x:c r="G2" s="6"/>
-      <x:c r="H2" s="6"/>
+      <x:c r="A2" s="25" t="str">
+        <x:v>状态：字段可见性 PASS｜共享模型字段树27/27可见；B已审核（2026-08-25）；G2仍需其他门槛闭环。</x:v>
+      </x:c>
+      <x:c r="B2" s="25"/>
+      <x:c r="C2" s="25"/>
+      <x:c r="D2" s="25"/>
+      <x:c r="E2" s="25"/>
+      <x:c r="F2" s="25"/>
+      <x:c r="G2" s="25"/>
+      <x:c r="H2" s="25"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>只读输入：18张正式工作簿 + 3张控制工作簿。离线读数不等于Smartbi平台已完成。</x:v>
+        <x:v>边界：仅证明字段存在/可见，未执行数据值查询、页面搭建或模型修改；A/B共用账号为既定前提。</x:v>
       </x:c>
       <x:c r="B3" s="9"/>
       <x:c r="C3" s="9"/>
@@ -18210,13 +18238,13 @@
         <x:v>离线存在</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>B可读(人工)</x:v>
+        <x:v>模型树可见（B复核）</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
-        <x:v>B可写(人工)</x:v>
+        <x:v>独立不可写</x:v>
       </x:c>
       <x:c r="H5" s="20" t="str">
-        <x:v>最终判定(公式)</x:v>
+        <x:v>字段判定</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -18235,11 +18263,15 @@
       <x:c r="E6" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F6" s="23"/>
-      <x:c r="G6" s="23"/>
-      <x:c r="H6" s="17" t="str">
-        <x:f>IF(OR(F6="",G6=""),"待人工",IF(AND(F6="是",G6="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F6" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G6" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H6" s="27" t="str">
+        <x:f>IF(F6="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -18258,11 +18290,15 @@
       <x:c r="E7" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F7" s="23"/>
-      <x:c r="G7" s="23"/>
-      <x:c r="H7" s="21" t="str">
-        <x:f>IF(OR(F7="",G7=""),"待人工",IF(AND(F7="是",G7="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F7" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G7" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H7" s="27" t="str">
+        <x:f>IF(F7="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -18281,11 +18317,15 @@
       <x:c r="E8" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F8" s="23"/>
-      <x:c r="G8" s="23"/>
-      <x:c r="H8" s="17" t="str">
-        <x:f>IF(OR(F8="",G8=""),"待人工",IF(AND(F8="是",G8="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F8" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G8" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H8" s="27" t="str">
+        <x:f>IF(F8="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -18304,11 +18344,15 @@
       <x:c r="E9" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F9" s="23"/>
-      <x:c r="G9" s="23"/>
-      <x:c r="H9" s="21" t="str">
-        <x:f>IF(OR(F9="",G9=""),"待人工",IF(AND(F9="是",G9="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F9" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G9" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H9" s="27" t="str">
+        <x:f>IF(F9="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -18327,11 +18371,15 @@
       <x:c r="E10" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F10" s="23"/>
-      <x:c r="G10" s="23"/>
-      <x:c r="H10" s="17" t="str">
-        <x:f>IF(OR(F10="",G10=""),"待人工",IF(AND(F10="是",G10="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F10" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H10" s="27" t="str">
+        <x:f>IF(F10="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -18350,11 +18398,15 @@
       <x:c r="E11" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F11" s="23"/>
-      <x:c r="G11" s="23"/>
-      <x:c r="H11" s="21" t="str">
-        <x:f>IF(OR(F11="",G11=""),"待人工",IF(AND(F11="是",G11="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F11" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G11" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H11" s="27" t="str">
+        <x:f>IF(F11="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -18373,11 +18425,15 @@
       <x:c r="E12" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F12" s="23"/>
-      <x:c r="G12" s="23"/>
-      <x:c r="H12" s="17" t="str">
-        <x:f>IF(OR(F12="",G12=""),"待人工",IF(AND(F12="是",G12="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F12" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G12" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H12" s="27" t="str">
+        <x:f>IF(F12="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -18396,11 +18452,15 @@
       <x:c r="E13" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F13" s="23"/>
-      <x:c r="G13" s="23"/>
-      <x:c r="H13" s="21" t="str">
-        <x:f>IF(OR(F13="",G13=""),"待人工",IF(AND(F13="是",G13="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F13" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G13" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H13" s="27" t="str">
+        <x:f>IF(F13="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -18419,11 +18479,15 @@
       <x:c r="E14" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F14" s="23"/>
-      <x:c r="G14" s="23"/>
-      <x:c r="H14" s="17" t="str">
-        <x:f>IF(OR(F14="",G14=""),"待人工",IF(AND(F14="是",G14="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F14" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G14" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H14" s="27" t="str">
+        <x:f>IF(F14="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -18442,11 +18506,15 @@
       <x:c r="E15" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F15" s="23"/>
-      <x:c r="G15" s="23"/>
-      <x:c r="H15" s="21" t="str">
-        <x:f>IF(OR(F15="",G15=""),"待人工",IF(AND(F15="是",G15="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F15" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G15" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H15" s="27" t="str">
+        <x:f>IF(F15="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -18465,11 +18533,15 @@
       <x:c r="E16" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F16" s="23"/>
-      <x:c r="G16" s="23"/>
-      <x:c r="H16" s="17" t="str">
-        <x:f>IF(OR(F16="",G16=""),"待人工",IF(AND(F16="是",G16="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F16" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G16" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H16" s="27" t="str">
+        <x:f>IF(F16="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -18488,11 +18560,15 @@
       <x:c r="E17" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F17" s="23"/>
-      <x:c r="G17" s="23"/>
-      <x:c r="H17" s="21" t="str">
-        <x:f>IF(OR(F17="",G17=""),"待人工",IF(AND(F17="是",G17="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F17" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G17" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H17" s="27" t="str">
+        <x:f>IF(F17="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -18511,11 +18587,15 @@
       <x:c r="E18" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F18" s="23"/>
-      <x:c r="G18" s="23"/>
-      <x:c r="H18" s="17" t="str">
-        <x:f>IF(OR(F18="",G18=""),"待人工",IF(AND(F18="是",G18="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F18" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G18" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H18" s="27" t="str">
+        <x:f>IF(F18="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -18534,11 +18614,15 @@
       <x:c r="E19" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F19" s="23"/>
-      <x:c r="G19" s="23"/>
-      <x:c r="H19" s="21" t="str">
-        <x:f>IF(OR(F19="",G19=""),"待人工",IF(AND(F19="是",G19="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F19" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G19" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H19" s="27" t="str">
+        <x:f>IF(F19="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -18557,11 +18641,15 @@
       <x:c r="E20" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F20" s="23"/>
-      <x:c r="G20" s="23"/>
-      <x:c r="H20" s="17" t="str">
-        <x:f>IF(OR(F20="",G20=""),"待人工",IF(AND(F20="是",G20="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F20" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G20" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H20" s="27" t="str">
+        <x:f>IF(F20="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -18580,11 +18668,15 @@
       <x:c r="E21" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F21" s="23"/>
-      <x:c r="G21" s="23"/>
-      <x:c r="H21" s="21" t="str">
-        <x:f>IF(OR(F21="",G21=""),"待人工",IF(AND(F21="是",G21="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F21" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G21" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H21" s="27" t="str">
+        <x:f>IF(F21="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -18603,11 +18695,15 @@
       <x:c r="E22" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F22" s="23"/>
-      <x:c r="G22" s="23"/>
-      <x:c r="H22" s="17" t="str">
-        <x:f>IF(OR(F22="",G22=""),"待人工",IF(AND(F22="是",G22="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F22" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G22" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H22" s="27" t="str">
+        <x:f>IF(F22="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -18626,11 +18722,15 @@
       <x:c r="E23" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F23" s="23"/>
-      <x:c r="G23" s="23"/>
-      <x:c r="H23" s="21" t="str">
-        <x:f>IF(OR(F23="",G23=""),"待人工",IF(AND(F23="是",G23="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F23" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G23" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H23" s="27" t="str">
+        <x:f>IF(F23="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -18649,11 +18749,15 @@
       <x:c r="E24" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F24" s="23"/>
-      <x:c r="G24" s="23"/>
-      <x:c r="H24" s="17" t="str">
-        <x:f>IF(OR(F24="",G24=""),"待人工",IF(AND(F24="是",G24="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F24" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G24" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H24" s="27" t="str">
+        <x:f>IF(F24="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -18672,11 +18776,15 @@
       <x:c r="E25" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F25" s="23"/>
-      <x:c r="G25" s="23"/>
-      <x:c r="H25" s="21" t="str">
-        <x:f>IF(OR(F25="",G25=""),"待人工",IF(AND(F25="是",G25="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F25" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G25" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H25" s="27" t="str">
+        <x:f>IF(F25="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -18695,11 +18803,15 @@
       <x:c r="E26" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F26" s="23"/>
-      <x:c r="G26" s="23"/>
-      <x:c r="H26" s="17" t="str">
-        <x:f>IF(OR(F26="",G26=""),"待人工",IF(AND(F26="是",G26="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F26" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G26" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H26" s="27" t="str">
+        <x:f>IF(F26="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -18718,11 +18830,15 @@
       <x:c r="E27" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F27" s="23"/>
-      <x:c r="G27" s="23"/>
-      <x:c r="H27" s="21" t="str">
-        <x:f>IF(OR(F27="",G27=""),"待人工",IF(AND(F27="是",G27="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F27" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G27" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H27" s="27" t="str">
+        <x:f>IF(F27="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -18741,11 +18857,15 @@
       <x:c r="E28" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F28" s="23"/>
-      <x:c r="G28" s="23"/>
-      <x:c r="H28" s="17" t="str">
-        <x:f>IF(OR(F28="",G28=""),"待人工",IF(AND(F28="是",G28="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F28" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G28" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H28" s="27" t="str">
+        <x:f>IF(F28="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -18764,11 +18884,15 @@
       <x:c r="E29" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F29" s="23"/>
-      <x:c r="G29" s="23"/>
-      <x:c r="H29" s="21" t="str">
-        <x:f>IF(OR(F29="",G29=""),"待人工",IF(AND(F29="是",G29="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F29" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G29" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H29" s="27" t="str">
+        <x:f>IF(F29="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -18787,11 +18911,15 @@
       <x:c r="E30" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F30" s="23"/>
-      <x:c r="G30" s="23"/>
-      <x:c r="H30" s="17" t="str">
-        <x:f>IF(OR(F30="",G30=""),"待人工",IF(AND(F30="是",G30="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F30" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G30" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H30" s="27" t="str">
+        <x:f>IF(F30="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -18810,11 +18938,15 @@
       <x:c r="E31" s="21" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F31" s="23"/>
-      <x:c r="G31" s="23"/>
-      <x:c r="H31" s="21" t="str">
-        <x:f>IF(OR(F31="",G31=""),"待人工",IF(AND(F31="是",G31="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F31" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G31" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H31" s="27" t="str">
+        <x:f>IF(F31="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -18833,11 +18965,15 @@
       <x:c r="E32" s="17" t="str">
         <x:v>OFFLINE_PASS</x:v>
       </x:c>
-      <x:c r="F32" s="23"/>
-      <x:c r="G32" s="23"/>
-      <x:c r="H32" s="17" t="str">
-        <x:f>IF(OR(F32="",G32=""),"待人工",IF(AND(F32="是",G32="否"),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+      <x:c r="F32" s="23" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="G32" s="23" t="str">
+        <x:v>不适用（共用账号）</x:v>
+      </x:c>
+      <x:c r="H32" s="27" t="str">
+        <x:f>IF(F32="是","PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
